--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0235.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0235.xlsx
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Tăng Tốc Nào! Cuộc Race Startorch!</t>
+          <t>Tăng Tốc Nào! Cuộc Đua Startorch!</t>
         </is>
       </c>
     </row>
